--- a/branches/rik-branch/StructureDefinition-timestamp.xlsx
+++ b/branches/rik-branch/StructureDefinition-timestamp.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-27T11:44:34+00:00</t>
+    <t>2022-09-27T11:44:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/rik-branch/StructureDefinition-timestamp.xlsx
+++ b/branches/rik-branch/StructureDefinition-timestamp.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-27T11:44:59+00:00</t>
+    <t>2022-09-27T11:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/rik-branch/StructureDefinition-timestamp.xlsx
+++ b/branches/rik-branch/StructureDefinition-timestamp.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-27T11:47:03+00:00</t>
+    <t>2022-09-27T11:47:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/rik-branch/StructureDefinition-timestamp.xlsx
+++ b/branches/rik-branch/StructureDefinition-timestamp.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-27T11:47:40+00:00</t>
+    <t>2022-09-27T11:55:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/rik-branch/StructureDefinition-timestamp.xlsx
+++ b/branches/rik-branch/StructureDefinition-timestamp.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2022-09-27T11:55:05+00:00</t>
+    <t>2022-09-27T11:56:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
